--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -19469,16 +19469,16 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O115" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0.855765153948111</v>
+        <v>0.8520923421285913</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -22729,16 +22729,16 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="O135" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>0.9549310730751454</v>
+        <v>0.9659495085337048</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23273,16 +23273,16 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O138" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>0.04263533832342501</v>
+        <v>0.04457330824721705</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -25693,16 +25693,16 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="O153" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q153" t="n">
         <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>0.1101843545855937</v>
+        <v>0.139566849141752</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26237,16 +26237,16 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O156" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q156" t="n">
         <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10973</v>
+        <v>10987</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -27181,16 +27181,16 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O159" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q159" t="n">
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>0.1836405909759895</v>
+        <v>0.1873134027955093</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -28495,6 +28495,154 @@
       <c r="BC166" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>30</v>
+      </c>
+      <c r="O167" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.02450425222697299</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28531,7 +28679,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -28614,7 +28762,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -28624,7 +28772,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -28676,7 +28824,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11006</v>
+        <v>11037</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>161</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>135</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>1.498701458447447</v>
       </c>
@@ -1454,9 +1448,6 @@
       <c r="O6" t="n">
         <v>64</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>1.138437869353048</v>
       </c>
@@ -1850,9 +1841,6 @@
       <c r="O8" t="n">
         <v>16</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.2168432448314735</v>
       </c>
@@ -1998,9 +1986,6 @@
       <c r="O9" t="n">
         <v>27</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.05232518794238524</v>
       </c>
@@ -2146,9 +2131,6 @@
       <c r="O10" t="n">
         <v>83</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>1.46824993541027</v>
       </c>
@@ -2791,7 +2773,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -2938,9 +2920,6 @@
       <c r="O14" t="n">
         <v>156</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>1.457801346812202</v>
       </c>
@@ -4962,9 +4941,6 @@
       <c r="O27" t="n">
         <v>142</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5355,9 +5331,6 @@
       <c r="O29" t="n">
         <v>126</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>1.398788027884284</v>
       </c>
@@ -5503,9 +5476,6 @@
       <c r="O30" t="n">
         <v>47</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.8360403103061447</v>
       </c>
@@ -5899,9 +5869,6 @@
       <c r="O32" t="n">
         <v>13</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.1761851364255722</v>
       </c>
@@ -6047,9 +6014,6 @@
       <c r="O33" t="n">
         <v>42</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.08139473679926593</v>
       </c>
@@ -6195,9 +6159,6 @@
       <c r="O34" t="n">
         <v>77</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>1.36211138586254</v>
       </c>
@@ -6840,7 +6801,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -6987,9 +6948,6 @@
       <c r="O38" t="n">
         <v>135</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>1.261558857818252</v>
       </c>
@@ -8863,9 +8821,6 @@
       <c r="O50" t="n">
         <v>165</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9256,9 +9211,6 @@
       <c r="O52" t="n">
         <v>106</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>1.176758182188366</v>
       </c>
@@ -9404,9 +9356,6 @@
       <c r="O53" t="n">
         <v>81</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>1.440835428399951</v>
       </c>
@@ -9800,9 +9749,6 @@
       <c r="O55" t="n">
         <v>10</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.1355270280196709</v>
       </c>
@@ -9948,9 +9894,6 @@
       <c r="O56" t="n">
         <v>43</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.08333270672305797</v>
       </c>
@@ -10096,9 +10039,6 @@
       <c r="O57" t="n">
         <v>74</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>1.309042111088675</v>
       </c>
@@ -10741,7 +10681,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -10888,9 +10828,6 @@
       <c r="O61" t="n">
         <v>119</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>1.112040770965718</v>
       </c>
@@ -12616,9 +12553,6 @@
       <c r="O72" t="n">
         <v>153</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.5619402083865279</v>
       </c>
@@ -12764,9 +12698,6 @@
       <c r="O73" t="n">
         <v>175</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="S73" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13157,9 +13088,6 @@
       <c r="O75" t="n">
         <v>101</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>1.121250720764387</v>
       </c>
@@ -13305,9 +13233,6 @@
       <c r="O76" t="n">
         <v>89</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>1.583140162069082</v>
       </c>
@@ -13701,9 +13626,6 @@
       <c r="O78" t="n">
         <v>12</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.1626324336236051</v>
       </c>
@@ -13849,9 +13771,6 @@
       <c r="O79" t="n">
         <v>59</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.1143402255037307</v>
       </c>
@@ -13997,9 +13916,6 @@
       <c r="O80" t="n">
         <v>84</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>1.485939693668225</v>
       </c>
@@ -14393,9 +14309,6 @@
       <c r="O82" t="n">
         <v>37</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.6997663725945767</v>
       </c>
@@ -14642,7 +14555,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -14789,9 +14702,6 @@
       <c r="O84" t="n">
         <v>145</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>1.355007662101085</v>
       </c>
@@ -15185,9 +15095,6 @@
       <c r="O86" t="n">
         <v>22</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.09560523382161172</v>
       </c>
@@ -16517,9 +16424,6 @@
       <c r="O95" t="n">
         <v>211</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.7749632939186758</v>
       </c>
@@ -16665,9 +16569,6 @@
       <c r="O96" t="n">
         <v>150</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17058,9 +16959,6 @@
       <c r="O98" t="n">
         <v>68</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.7549014753661216</v>
       </c>
@@ -17206,9 +17104,6 @@
       <c r="O99" t="n">
         <v>77</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>1.369683061565386</v>
       </c>
@@ -17602,9 +17497,6 @@
       <c r="O101" t="n">
         <v>6</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.08131621681180255</v>
       </c>
@@ -17750,9 +17642,6 @@
       <c r="O102" t="n">
         <v>46</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.0891466164944341</v>
       </c>
@@ -17898,9 +17787,6 @@
       <c r="O103" t="n">
         <v>71</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>1.255972836314809</v>
       </c>
@@ -18294,9 +18180,6 @@
       <c r="O105" t="n">
         <v>55</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>1.040193256559506</v>
       </c>
@@ -18543,7 +18426,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -18690,9 +18573,6 @@
       <c r="O107" t="n">
         <v>136</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>1.270903738246535</v>
       </c>
@@ -19086,9 +18966,6 @@
       <c r="O109" t="n">
         <v>31</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.1347164658395438</v>
       </c>
@@ -20566,9 +20443,6 @@
       <c r="O119" t="n">
         <v>105</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.03008290039407855</v>
       </c>
@@ -20714,9 +20588,6 @@
       <c r="O120" t="n">
         <v>232</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.8520923421285913</v>
       </c>
@@ -20862,9 +20733,6 @@
       <c r="O121" t="n">
         <v>46</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.5106686451006117</v>
       </c>
@@ -21010,9 +20878,6 @@
       <c r="O122" t="n">
         <v>52</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.9249807688493514</v>
       </c>
@@ -21406,9 +21271,6 @@
       <c r="O124" t="n">
         <v>7</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.09486891961376966</v>
       </c>
@@ -21554,9 +21416,6 @@
       <c r="O125" t="n">
         <v>27</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.05232518794238524</v>
       </c>
@@ -21702,9 +21561,6 @@
       <c r="O126" t="n">
         <v>49</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.8667981546397979</v>
       </c>
@@ -22098,9 +21954,6 @@
       <c r="O128" t="n">
         <v>68</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>1.286057117200844</v>
       </c>
@@ -22347,7 +22200,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -22494,9 +22347,6 @@
       <c r="O130" t="n">
         <v>85</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.7943148364040844</v>
       </c>
@@ -22890,9 +22740,6 @@
       <c r="O132" t="n">
         <v>21</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.09125954137517482</v>
       </c>
@@ -23038,9 +22885,6 @@
       <c r="O133" t="n">
         <v>50</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.04084042037828831</v>
       </c>
@@ -23186,9 +23030,6 @@
       <c r="O134" t="n">
         <v>92</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.02635835082147835</v>
       </c>
@@ -23334,9 +23175,6 @@
       <c r="O135" t="n">
         <v>43</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.03512276152532795</v>
       </c>
@@ -23482,9 +23320,6 @@
       <c r="O136" t="n">
         <v>100</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.02865038132769385</v>
       </c>
@@ -23630,9 +23465,6 @@
       <c r="O137" t="n">
         <v>34</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.02777148585723605</v>
       </c>
@@ -23778,9 +23610,6 @@
       <c r="O138" t="n">
         <v>97</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.02779086988786304</v>
       </c>
@@ -23926,9 +23755,6 @@
       <c r="O139" t="n">
         <v>26</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.02123701859670992</v>
       </c>
@@ -24074,9 +23900,6 @@
       <c r="O140" t="n">
         <v>87</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.02492583175509365</v>
       </c>
@@ -24222,9 +24045,6 @@
       <c r="O141" t="n">
         <v>267</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.980640755811784</v>
       </c>
@@ -24370,9 +24190,6 @@
       <c r="O142" t="n">
         <v>28</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.4980665678419585</v>
       </c>
@@ -24766,9 +24583,6 @@
       <c r="O144" t="n">
         <v>23</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.04457330824721705</v>
       </c>
@@ -24909,16 +24723,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O145" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="R145" t="n">
-        <v>0.6899005720602475</v>
+        <v>0.7075903303182025</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -25071,10 +24882,10 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O146" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
@@ -25310,9 +25121,6 @@
       <c r="O147" t="n">
         <v>51</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.4765889018424507</v>
       </c>
@@ -25706,9 +25514,6 @@
       <c r="O149" t="n">
         <v>16</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.06953107914299034</v>
       </c>
@@ -25854,9 +25659,6 @@
       <c r="O150" t="n">
         <v>35</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.02858829426480182</v>
       </c>
@@ -26002,9 +25804,6 @@
       <c r="O151" t="n">
         <v>79</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.02263380124887814</v>
       </c>
@@ -26150,9 +25949,6 @@
       <c r="O152" t="n">
         <v>32</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.02613786904210452</v>
       </c>
@@ -26298,9 +26094,6 @@
       <c r="O153" t="n">
         <v>74</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.02120128218249345</v>
       </c>
@@ -26446,9 +26239,6 @@
       <c r="O154" t="n">
         <v>18</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.01470255133618379</v>
       </c>
@@ -26594,9 +26384,6 @@
       <c r="O155" t="n">
         <v>87</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.02492583175509365</v>
       </c>
@@ -26742,9 +26529,6 @@
       <c r="O156" t="n">
         <v>28</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.02287063541184146</v>
       </c>
@@ -26890,9 +26674,6 @@
       <c r="O157" t="n">
         <v>72</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.02062827455593957</v>
       </c>
@@ -27038,9 +26819,6 @@
       <c r="O158" t="n">
         <v>25</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.02042021018914416</v>
       </c>
@@ -27186,9 +26964,6 @@
       <c r="O159" t="n">
         <v>51</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.1873134027955093</v>
       </c>
@@ -27334,9 +27109,6 @@
       <c r="O160" t="n">
         <v>4</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.07115236683456549</v>
       </c>
@@ -27725,16 +27497,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O162" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q162" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R162" t="n">
-        <v>0.01356578946654432</v>
+        <v>0.01744172931412841</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -27873,16 +27642,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O163" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q163" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R163" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.2122770990954608</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -28035,10 +27801,10 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O164" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="U164" t="inlineStr">
         <is>
@@ -28274,9 +28040,6 @@
       <c r="O165" t="n">
         <v>1</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -28422,9 +28185,6 @@
       <c r="O166" t="n">
         <v>67</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.01919575548955488</v>
       </c>
@@ -28570,9 +28330,6 @@
       <c r="O167" t="n">
         <v>30</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.02450425222697299</v>
       </c>
@@ -28643,6 +28400,151 @@
       <c r="BC167" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>58</v>
+      </c>
+      <c r="O168" t="n">
+        <v>58</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.01661722117006243</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
+      <c r="AT168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -28762,7 +28664,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -28772,7 +28674,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11">
@@ -28824,7 +28726,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11037</v>
+        <v>11109</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -27104,13 +27104,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O160" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R160" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -27263,10 +27263,10 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O161" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11109</v>
+        <v>11110</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -25509,13 +25509,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O149" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R149" t="n">
-        <v>0.06953107914299034</v>
+        <v>0.08256815648230102</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -27497,13 +27497,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O162" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R162" t="n">
-        <v>0.01744172931412841</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11110</v>
+        <v>11114</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -24040,13 +24040,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O141" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="R141" t="n">
-        <v>0.980640755811784</v>
+        <v>0.9879863794508235</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -26959,13 +26959,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="O159" t="n">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="R159" t="n">
-        <v>0.1873134027955093</v>
+        <v>0.2901521337420634</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -27104,13 +27104,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O160" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R160" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.1067285502518482</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -27263,10 +27263,10 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O161" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11114</v>
+        <v>11145</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O4" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O27" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O28" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -12693,10 +12693,10 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O73" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -12849,10 +12849,10 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O74" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -16564,10 +16564,10 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O96" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -16720,10 +16720,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O97" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -20689,12 +20689,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20728,81 +20728,92 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="O121" t="n">
-        <v>46</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0.5106686451006117</v>
+        <v>109</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_PNEUMOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_PNEUMOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20829,17 +20840,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -20873,22 +20884,39 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="O122" t="n">
-        <v>52</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0.9249807688493514</v>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>109</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1390</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_PNEUMOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_PNEUMOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Streptococcus Pneumoniae, Invasive</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -20896,6 +20924,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary invasive pneumococcal disease notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>1</v>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -20908,12 +20994,12 @@
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1390</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_PNEUMOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT122" t="n">
@@ -20921,47 +21007,47 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20988,17 +21074,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21032,170 +21118,81 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="O123" t="n">
-        <v>52</v>
-      </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>Streptococcus pneumoniae</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG123" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN123" t="b">
-        <v>1</v>
+        <v>46</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.5106686451006117</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -21227,12 +21224,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21266,81 +21263,95 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="O124" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="R124" t="n">
-        <v>0.09486891961376966</v>
+        <v>0.9249807688493514</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21367,17 +21378,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21411,81 +21422,170 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="O125" t="n">
-        <v>27</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0.05232518794238524</v>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>52</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Streptococcus pneumoniae</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21517,12 +21617,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21556,95 +21656,81 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="O126" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="R126" t="n">
-        <v>0.8667981546397979</v>
+        <v>0.09486891961376966</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21671,17 +21757,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21715,170 +21801,81 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="O127" t="n">
-        <v>49</v>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>Syst. pneumokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD127" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE127" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF127" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG127" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN127" t="b">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.05232518794238524</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21910,12 +21907,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -21949,13 +21946,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="O128" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="R128" t="n">
-        <v>1.286057117200844</v>
+        <v>0.8667981546397979</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -21964,7 +21961,7 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -21989,7 +21986,7 @@
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT128" t="n">
@@ -22002,42 +21999,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22069,12 +22066,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22108,29 +22105,29 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="O129" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Syst. pneumokokksykdom</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -22140,7 +22137,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -22155,7 +22152,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
@@ -22190,17 +22187,17 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly invasive pneumococcal disease notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -22223,7 +22220,7 @@
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT129" t="n">
@@ -22236,42 +22233,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22303,12 +22300,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22342,13 +22339,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="O130" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="R130" t="n">
-        <v>0.7943148364040844</v>
+        <v>1.286057117200844</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -22357,7 +22354,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -22382,7 +22379,7 @@
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT130" t="n">
@@ -22395,42 +22392,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22462,12 +22459,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22501,29 +22498,29 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="O131" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>Invasiv pneumokockinfektion</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="Y131" t="inlineStr">
@@ -22533,7 +22530,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -22548,7 +22545,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
@@ -22583,17 +22580,17 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+          <t>New Zealand PHF Science monthly invasive pneumococcal disease notifications.</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -22616,7 +22613,7 @@
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT131" t="n">
@@ -22629,42 +22626,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22696,12 +22693,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -22735,81 +22732,95 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="O132" t="n">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="R132" t="n">
-        <v>0.09125954137517482</v>
+        <v>0.7943148364040844</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22836,17 +22847,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -22871,7 +22882,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -22880,81 +22891,170 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="O133" t="n">
-        <v>50</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0.04084042037828831</v>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>85</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>Invasiv pneumokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN133" t="b">
+        <v>1</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22986,12 +23086,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -23016,7 +23116,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -23025,13 +23125,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="O134" t="n">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="R134" t="n">
-        <v>0.02635835082147835</v>
+        <v>0.09125954137517482</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23064,42 +23164,42 @@
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23161,7 +23261,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -23170,13 +23270,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="O135" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="R135" t="n">
-        <v>0.03512276152532795</v>
+        <v>0.04084042037828831</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23306,7 +23406,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -23315,13 +23415,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="O136" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="R136" t="n">
-        <v>0.02865038132769385</v>
+        <v>0.02635835082147835</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23451,7 +23551,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -23460,13 +23560,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="O137" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="R137" t="n">
-        <v>0.02777148585723605</v>
+        <v>0.03512276152532795</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -23596,7 +23696,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -23605,13 +23705,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O138" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="R138" t="n">
-        <v>0.02779086988786304</v>
+        <v>0.02865038132769385</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23741,7 +23841,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -23750,13 +23850,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="O139" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="R139" t="n">
-        <v>0.02123701859670992</v>
+        <v>0.02777148585723605</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -23886,7 +23986,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -23895,13 +23995,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="O140" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="R140" t="n">
-        <v>0.02492583175509365</v>
+        <v>0.02779086988786304</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -24001,12 +24101,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24031,22 +24131,22 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N141" t="n">
-        <v>269</v>
+        <v>26</v>
       </c>
       <c r="O141" t="n">
-        <v>269</v>
+        <v>26</v>
       </c>
       <c r="R141" t="n">
-        <v>0.9879863794508235</v>
+        <v>0.02123701859670992</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -24079,42 +24179,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24146,12 +24246,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24176,104 +24276,90 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N142" t="n">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="O142" t="n">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="R142" t="n">
-        <v>0.4980665678419585</v>
+        <v>0.02492583175509365</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24300,17 +24386,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24344,170 +24430,81 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>28</v>
+        <v>269</v>
       </c>
       <c r="O143" t="n">
-        <v>28</v>
-      </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>Streptococcus pneumoniae</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD143" t="inlineStr">
+        <v>269</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.9879863794508235</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE143" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF143" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG143" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN143" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP143" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="AT143" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV143" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24539,12 +24536,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24578,81 +24575,95 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="O144" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="R144" t="n">
-        <v>0.04457330824721705</v>
+        <v>0.4980665678419585</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24679,17 +24690,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -24723,22 +24734,39 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O145" t="n">
-        <v>40</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0.7075903303182025</v>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>28</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Streptococcus pneumoniae</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -24746,6 +24774,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -24758,12 +24844,12 @@
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT145" t="n">
@@ -24771,47 +24857,47 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24838,17 +24924,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -24882,170 +24968,81 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="O146" t="n">
-        <v>40</v>
-      </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V146" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>Syst. pneumokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA146" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD146" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE146" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF146" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG146" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
-        </is>
-      </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN146" t="b">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0.04457330824721705</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -25077,12 +25074,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25116,13 +25113,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="O147" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="R147" t="n">
-        <v>0.4765889018424507</v>
+        <v>0.7075903303182025</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -25131,7 +25128,7 @@
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -25156,7 +25153,7 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT147" t="n">
@@ -25169,42 +25166,42 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25236,12 +25233,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -25275,29 +25272,29 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="O148" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>Invasiv pneumokockinfektion</t>
+          <t>Syst. pneumokokksykdom</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
@@ -25322,7 +25319,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
@@ -25357,17 +25354,17 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -25390,7 +25387,7 @@
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT148" t="n">
@@ -25403,42 +25400,42 @@
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25470,12 +25467,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25509,81 +25506,95 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="O149" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="R149" t="n">
-        <v>0.08256815648230102</v>
+        <v>0.4765889018424507</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25610,17 +25621,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25645,7 +25656,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25654,81 +25665,170 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="O150" t="n">
-        <v>35</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0.02858829426480182</v>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>51</v>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Invasiv pneumokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN150" t="b">
+        <v>1</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25760,12 +25860,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25790,7 +25890,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25799,13 +25899,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="O151" t="n">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="R151" t="n">
-        <v>0.02263380124887814</v>
+        <v>0.08256815648230102</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25838,42 +25938,42 @@
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25935,7 +26035,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -25944,13 +26044,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O152" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R152" t="n">
-        <v>0.02613786904210452</v>
+        <v>0.02858829426480182</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -26080,7 +26180,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -26089,13 +26189,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="O153" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="R153" t="n">
-        <v>0.02120128218249345</v>
+        <v>0.02263380124887814</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26225,7 +26325,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -26234,13 +26334,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="O154" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="R154" t="n">
-        <v>0.01470255133618379</v>
+        <v>0.02613786904210452</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26370,7 +26470,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -26379,13 +26479,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="O155" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="R155" t="n">
-        <v>0.02492583175509365</v>
+        <v>0.02120128218249345</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26515,7 +26615,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -26524,13 +26624,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="O156" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="R156" t="n">
-        <v>0.02287063541184146</v>
+        <v>0.01470255133618379</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26660,7 +26760,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -26669,13 +26769,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="O157" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="R157" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.02492583175509365</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -26805,7 +26905,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -26814,13 +26914,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O158" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R158" t="n">
-        <v>0.02042021018914416</v>
+        <v>0.02287063541184146</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -26920,12 +27020,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -26950,22 +27050,22 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N159" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="O159" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="R159" t="n">
-        <v>0.2901521337420634</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -26998,42 +27098,42 @@
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27065,12 +27165,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27095,104 +27195,90 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N160" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="O160" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R160" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.02042021018914416</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27219,17 +27305,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27263,170 +27349,81 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>6</v>
+        <v>113</v>
       </c>
       <c r="O161" t="n">
-        <v>6</v>
-      </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>Streptococcus pneumoniae</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD161" t="inlineStr">
+        <v>113</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0.4150277356057363</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE161" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF161" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG161" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN161" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP161" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ161" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="AT161" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV161" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27458,12 +27455,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27497,81 +27494,95 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O162" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R162" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.1067285502518482</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27598,17 +27609,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27642,22 +27653,39 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O163" t="n">
-        <v>12</v>
-      </c>
-      <c r="R163" t="n">
-        <v>0.2122770990954608</v>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Streptococcus pneumoniae</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -27665,6 +27693,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>1</v>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -27677,12 +27763,12 @@
       </c>
       <c r="AQ163" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT163" t="n">
@@ -27690,47 +27776,47 @@
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27757,17 +27843,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -27801,170 +27887,81 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O164" t="n">
-        <v>12</v>
-      </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W164" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>Syst. pneumokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y164" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE164" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF164" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG164" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN164" t="b">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0.01937969923792046</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27996,12 +27993,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28035,81 +28032,95 @@
         </is>
       </c>
       <c r="N165" t="n">
+        <v>12</v>
+      </c>
+      <c r="O165" t="n">
+        <v>12</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.2122770990954608</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT165" t="n">
         <v>1</v>
       </c>
-      <c r="O165" t="n">
-        <v>1</v>
-      </c>
-      <c r="R165" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP165" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
-      <c r="AT165" t="n">
-        <v>0</v>
-      </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28136,17 +28147,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -28180,81 +28191,170 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="O166" t="n">
-        <v>67</v>
-      </c>
-      <c r="R166" t="n">
-        <v>0.01919575548955488</v>
-      </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>Syst. pneumokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN166" t="b">
+        <v>1</v>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28286,12 +28386,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -28316,7 +28416,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -28325,13 +28425,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O167" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="R167" t="n">
-        <v>0.02450425222697299</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -28364,42 +28464,42 @@
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -28461,7 +28561,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -28470,13 +28570,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="O168" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="R168" t="n">
-        <v>0.01661722117006243</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -28543,6 +28643,296 @@
         </is>
       </c>
       <c r="BC168" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>30</v>
+      </c>
+      <c r="O169" t="n">
+        <v>30</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0.02450425222697299</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr"/>
+      <c r="AT169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>58</v>
+      </c>
+      <c r="O170" t="n">
+        <v>58</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.01661722117006243</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
+      <c r="AT170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -28664,7 +29054,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
@@ -28674,7 +29064,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -28694,7 +29084,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -28726,7 +29116,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11145</v>
+        <v>11294</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -25899,13 +25899,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O151" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R151" t="n">
-        <v>0.08256815648230102</v>
+        <v>0.08691384892873792</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -28425,13 +28425,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R167" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11294</v>
+        <v>11296</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -24430,13 +24430,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O143" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R143" t="n">
-        <v>0.9879863794508235</v>
+        <v>0.9953320030898631</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -24968,13 +24968,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O146" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R146" t="n">
-        <v>0.04457330824721705</v>
+        <v>0.04844924809480115</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -27349,13 +27349,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="O161" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="R161" t="n">
-        <v>0.4150277356057363</v>
+        <v>0.4517558538009342</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -27494,13 +27494,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O162" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R162" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -27653,10 +27653,10 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O163" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
@@ -27887,13 +27887,13 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O164" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R164" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.02325563908550455</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -28935,6 +28935,151 @@
       <c r="BC170" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>18</v>
+      </c>
+      <c r="O171" t="n">
+        <v>18</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0.01470255133618379</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
+      <c r="AT171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28971,7 +29116,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -29054,7 +29199,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
@@ -29064,7 +29209,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -29116,7 +29261,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11296</v>
+        <v>11332</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -27494,13 +27494,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O162" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R162" t="n">
-        <v>0.142304733669131</v>
+        <v>0.1778809170864138</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -27653,10 +27653,10 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O163" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11332</v>
+        <v>11334</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -24430,13 +24430,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O143" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R143" t="n">
-        <v>0.9953320030898631</v>
+        <v>1.002677626728903</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -27349,13 +27349,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="O161" t="n">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="R161" t="n">
-        <v>0.4517558538009342</v>
+        <v>0.5435761492889289</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -27494,13 +27494,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O162" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R162" t="n">
-        <v>0.1778809170864138</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -27653,10 +27653,10 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O163" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
@@ -28032,13 +28032,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O165" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="R165" t="n">
-        <v>0.2122770990954608</v>
+        <v>0.3361054069011462</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -28191,10 +28191,10 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O166" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="U166" t="inlineStr">
         <is>
@@ -29080,6 +29080,151 @@
       <c r="BC171" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>76</v>
+      </c>
+      <c r="O172" t="n">
+        <v>76</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0.02177428980904733</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr"/>
+      <c r="AT172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29116,7 +29261,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29344,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
@@ -29209,7 +29354,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -29261,7 +29406,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11334</v>
+        <v>11445</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -27349,13 +27349,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="O161" t="n">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="R161" t="n">
-        <v>0.5435761492889289</v>
+        <v>0.5986683265817258</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -27494,13 +27494,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O162" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R162" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -27653,10 +27653,10 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O163" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11445</v>
+        <v>11461</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -24430,13 +24430,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O143" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R143" t="n">
-        <v>1.002677626728903</v>
+        <v>1.006350438548423</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -27349,13 +27349,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="O161" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="R161" t="n">
-        <v>0.5986683265817258</v>
+        <v>0.6243780093183643</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -27494,13 +27494,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O162" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R162" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -27653,10 +27653,10 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O163" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11461</v>
+        <v>11470</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -27349,13 +27349,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="O161" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R161" t="n">
-        <v>0.6243780093183643</v>
+        <v>0.6464148802354831</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11470</v>
+        <v>11476</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -24430,13 +24430,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="O143" t="n">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="R143" t="n">
-        <v>1.006350438548423</v>
+        <v>1.021041685826502</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -27349,13 +27349,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="O161" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="R161" t="n">
-        <v>0.6464148802354831</v>
+        <v>0.6721245629721216</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11476</v>
+        <v>11487</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -25467,12 +25467,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25506,13 +25506,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="O149" t="n">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="R149" t="n">
-        <v>0.4765889018424507</v>
+        <v>1.796697443148238</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -25546,7 +25546,7 @@
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT149" t="n">
@@ -25559,42 +25559,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25626,12 +25626,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25665,29 +25665,29 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="O150" t="n">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>Invasiv pneumokockinfektion</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="Y150" t="inlineStr">
@@ -25697,7 +25697,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -25712,7 +25712,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr">
@@ -25747,17 +25747,17 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+          <t>New Zealand PHF Science monthly invasive pneumococcal disease notifications.</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN150" t="b">
@@ -25780,7 +25780,7 @@
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT150" t="n">
@@ -25793,42 +25793,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25860,12 +25860,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25899,81 +25899,95 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="O151" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="R151" t="n">
-        <v>0.08691384892873792</v>
+        <v>0.4765889018424507</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26000,17 +26014,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26035,7 +26049,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -26044,81 +26058,170 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="O152" t="n">
-        <v>35</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0.02858829426480182</v>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>51</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Invasiv pneumokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN152" t="b">
+        <v>1</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26150,12 +26253,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26180,7 +26283,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -26189,13 +26292,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="O153" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="R153" t="n">
-        <v>0.02263380124887814</v>
+        <v>0.08691384892873792</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26228,42 +26331,42 @@
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -26325,7 +26428,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -26334,13 +26437,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O154" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R154" t="n">
-        <v>0.02613786904210452</v>
+        <v>0.02858829426480182</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26470,7 +26573,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -26479,13 +26582,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="O155" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="R155" t="n">
-        <v>0.02120128218249345</v>
+        <v>0.02263380124887814</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26615,7 +26718,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -26624,13 +26727,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="O156" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="R156" t="n">
-        <v>0.01470255133618379</v>
+        <v>0.02613786904210452</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26760,7 +26863,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -26769,13 +26872,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="O157" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="R157" t="n">
-        <v>0.02492583175509365</v>
+        <v>0.02120128218249345</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -26905,7 +27008,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -26914,13 +27017,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="O158" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="R158" t="n">
-        <v>0.02287063541184146</v>
+        <v>0.01470255133618379</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -27050,7 +27153,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -27059,13 +27162,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="O159" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="R159" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.02492583175509365</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -27195,7 +27298,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -27204,13 +27307,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O160" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R160" t="n">
-        <v>0.02042021018914416</v>
+        <v>0.02287063541184146</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -27310,12 +27413,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27340,22 +27443,22 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N161" t="n">
-        <v>183</v>
+        <v>72</v>
       </c>
       <c r="O161" t="n">
-        <v>183</v>
+        <v>72</v>
       </c>
       <c r="R161" t="n">
-        <v>0.6721245629721216</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -27388,42 +27491,42 @@
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27455,12 +27558,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27485,104 +27588,90 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N162" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="O162" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="R162" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.02042021018914416</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27609,17 +27698,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27653,170 +27742,81 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="O163" t="n">
-        <v>13</v>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="W163" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X163" t="inlineStr">
-        <is>
-          <t>Streptococcus pneumoniae</t>
-        </is>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD163" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.734562363903958</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE163" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF163" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG163" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH163" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ163" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK163" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
-        </is>
-      </c>
-      <c r="AM163" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN163" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP163" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="AT163" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV163" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27848,12 +27848,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -27887,81 +27887,95 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O164" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="R164" t="n">
-        <v>0.02325563908550455</v>
+        <v>0.3379737424641861</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
       <c r="AT164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27988,17 +28002,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28037,17 +28051,34 @@
       <c r="O165" t="n">
         <v>19</v>
       </c>
-      <c r="R165" t="n">
-        <v>0.3361054069011462</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Streptococcus pneumoniae</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -28055,6 +28086,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -28067,12 +28156,12 @@
       </c>
       <c r="AQ165" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT165" t="n">
@@ -28080,47 +28169,47 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28147,17 +28236,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -28191,170 +28280,81 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="O166" t="n">
-        <v>19</v>
-      </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>Syst. pneumokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE166" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF166" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG166" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN166" t="b">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.03100751878067274</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ166" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28386,12 +28386,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -28425,81 +28425,95 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="O167" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="R167" t="n">
-        <v>0.008691384892873792</v>
+        <v>0.4776234729647867</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28526,17 +28540,17 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -28570,81 +28584,170 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="O168" t="n">
-        <v>67</v>
-      </c>
-      <c r="R168" t="n">
-        <v>0.01919575548955488</v>
-      </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>Syst. pneumokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN168" t="b">
+        <v>1</v>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28676,12 +28779,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -28706,7 +28809,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -28715,13 +28818,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="O169" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="R169" t="n">
-        <v>0.02450425222697299</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -28754,42 +28857,42 @@
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -28851,7 +28954,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -28860,13 +28963,13 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="O170" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="R170" t="n">
-        <v>0.01661722117006243</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -28996,7 +29099,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -29005,13 +29108,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="O171" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="R171" t="n">
-        <v>0.01470255133618379</v>
+        <v>0.02450425222697299</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -29141,7 +29244,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -29150,13 +29253,13 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="O172" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="R172" t="n">
-        <v>0.02177428980904733</v>
+        <v>0.01661722117006243</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -29225,6 +29328,441 @@
       <c r="BC172" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>18</v>
+      </c>
+      <c r="O173" t="n">
+        <v>18</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0.01470255133618379</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr"/>
+      <c r="AT173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>76</v>
+      </c>
+      <c r="O174" t="n">
+        <v>76</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0.02177428980904733</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
+      <c r="AT174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>29</v>
+      </c>
+      <c r="O175" t="n">
+        <v>29</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0.02368744381940722</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr"/>
+      <c r="AT175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29261,7 +29799,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -29344,7 +29882,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10">
@@ -29354,7 +29892,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -29374,7 +29912,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -29406,7 +29944,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11487</v>
+        <v>11646</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -24430,13 +24430,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O143" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="R143" t="n">
-        <v>1.021041685826502</v>
+        <v>1.024714497646021</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -27742,13 +27742,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="O163" t="n">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="R163" t="n">
-        <v>0.734562363903958</v>
+        <v>0.7970001648357945</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -28280,13 +28280,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O166" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R166" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.03294548870446478</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11646</v>
+        <v>11665</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -35173,12 +35173,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -35212,13 +35212,13 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="O198" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R198" t="n">
-        <v>0.04844924809480115</v>
+        <v>0.2032905420295064</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -35251,42 +35251,42 @@
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -35318,12 +35318,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -35357,95 +35357,81 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="O199" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="R199" t="n">
-        <v>0.7075903303182025</v>
+        <v>0.04844924809480115</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35472,7 +35458,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -35521,98 +35507,23 @@
       <c r="O200" t="n">
         <v>40</v>
       </c>
+      <c r="R200" t="n">
+        <v>0.7075903303182025</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U200" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Syst. pneumokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
-        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
@@ -35706,17 +35617,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -35750,22 +35661,39 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="O201" t="n">
-        <v>95</v>
-      </c>
-      <c r="R201" t="n">
-        <v>1.796697443148238</v>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>40</v>
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Syst. pneumokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -35773,6 +35701,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN201" t="b">
+        <v>1</v>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -35790,7 +35776,7 @@
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT201" t="n">
@@ -35803,42 +35789,42 @@
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -35865,7 +35851,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -35914,98 +35900,23 @@
       <c r="O202" t="n">
         <v>95</v>
       </c>
+      <c r="R202" t="n">
+        <v>1.796697443148238</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U202" t="inlineStr">
         <is>
           <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>Invasive pneumococcal disease</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD202" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE202" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF202" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG202" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly invasive pneumococcal disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN202" t="b">
-        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
@@ -36099,17 +36010,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -36143,22 +36054,39 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="O203" t="n">
-        <v>51</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0.4765889018424507</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>95</v>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -36166,6 +36094,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly invasive pneumococcal disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -36183,7 +36169,7 @@
       </c>
       <c r="AS203" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT203" t="n">
@@ -36196,42 +36182,42 @@
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36258,7 +36244,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -36307,98 +36293,23 @@
       <c r="O204" t="n">
         <v>51</v>
       </c>
+      <c r="R204" t="n">
+        <v>0.4765889018424507</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U204" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>Invasiv pneumokockinfektion</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN204" t="b">
-        <v>1</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
@@ -36492,17 +36403,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -36536,81 +36447,170 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="O205" t="n">
-        <v>20</v>
-      </c>
-      <c r="R205" t="n">
-        <v>0.08691384892873792</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>51</v>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Invasiv pneumokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -36642,12 +36642,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -36672,7 +36672,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -36681,13 +36681,13 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="O206" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="R206" t="n">
-        <v>0.02858829426480182</v>
+        <v>0.08691384892873792</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -36720,42 +36720,42 @@
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -36787,12 +36787,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -36826,13 +36826,13 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="O207" t="n">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="R207" t="n">
-        <v>0.02263380124887814</v>
+        <v>0.02858829426480182</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -36865,42 +36865,42 @@
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36932,12 +36932,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -36962,7 +36962,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -36971,93 +36971,81 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="O208" t="n">
-        <v>4</v>
-      </c>
-      <c r="P208" t="n">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="R208" t="n">
-        <v>0.0677306302038819</v>
+        <v>0.02263380124887814</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA208" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37084,7 +37072,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -37136,98 +37124,18 @@
       <c r="P209" t="n">
         <v>4</v>
       </c>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R209" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD209" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE209" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG209" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN209" t="b">
-        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
@@ -37321,17 +37229,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -37356,7 +37264,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -37365,81 +37273,173 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="O210" t="n">
-        <v>32</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0.02613786904210452</v>
-      </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="P210" t="n">
+        <v>4</v>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN210" t="b">
+        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37471,12 +37471,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -37510,13 +37510,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="O211" t="n">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="R211" t="n">
-        <v>0.02120128218249345</v>
+        <v>0.02613786904210452</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -37549,42 +37549,42 @@
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37616,12 +37616,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -37646,7 +37646,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -37655,93 +37655,81 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="O212" t="n">
-        <v>1</v>
-      </c>
-      <c r="P212" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="R212" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.02120128218249345</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA212" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ212" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37768,7 +37756,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -37820,98 +37808,18 @@
       <c r="P213" t="n">
         <v>1</v>
       </c>
-      <c r="U213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W213" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R213" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD213" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE213" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF213" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG213" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ213" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK213" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM213" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN213" t="b">
-        <v>1</v>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
@@ -38005,17 +37913,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -38040,7 +37948,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -38049,81 +37957,173 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O214" t="n">
-        <v>18</v>
-      </c>
-      <c r="R214" t="n">
-        <v>0.01470255133618379</v>
-      </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P214" t="n">
+        <v>1</v>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN214" t="b">
+        <v>1</v>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38155,12 +38155,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -38194,13 +38194,13 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="O215" t="n">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="R215" t="n">
-        <v>0.02492583175509365</v>
+        <v>0.01470255133618379</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -38233,42 +38233,42 @@
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38300,12 +38300,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -38330,7 +38330,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -38339,93 +38339,81 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="O216" t="n">
-        <v>2</v>
-      </c>
-      <c r="P216" t="n">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="R216" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.02492583175509365</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA216" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ216" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38452,7 +38440,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -38504,98 +38492,18 @@
       <c r="P217" t="n">
         <v>2</v>
       </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y217" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R217" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD217" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE217" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF217" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG217" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN217" t="b">
-        <v>1</v>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
@@ -38689,17 +38597,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -38724,7 +38632,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -38733,81 +38641,173 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="O218" t="n">
-        <v>28</v>
-      </c>
-      <c r="R218" t="n">
-        <v>0.02287063541184146</v>
-      </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P218" t="n">
+        <v>2</v>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN218" t="b">
+        <v>1</v>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38839,12 +38839,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -38878,13 +38878,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="O219" t="n">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="R219" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.02287063541184146</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -38917,42 +38917,42 @@
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38984,12 +38984,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -39014,7 +39014,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -39023,13 +39023,13 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="O220" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="R220" t="n">
-        <v>0.02042021018914416</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -39062,42 +39062,42 @@
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39129,12 +39129,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -39168,93 +39168,81 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="O221" t="n">
-        <v>4</v>
-      </c>
-      <c r="P221" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="R221" t="n">
-        <v>0.0677306302038819</v>
+        <v>0.02042021018914416</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA221" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ221" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr"/>
       <c r="AT221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39281,7 +39269,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -39333,98 +39321,18 @@
       <c r="P222" t="n">
         <v>4</v>
       </c>
-      <c r="U222" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y222" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R222" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD222" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE222" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF222" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG222" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ222" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK222" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM222" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN222" t="b">
-        <v>1</v>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
@@ -39518,17 +39426,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -39553,90 +39461,182 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N223" t="n">
-        <v>217</v>
+        <v>4</v>
       </c>
       <c r="O223" t="n">
-        <v>217</v>
-      </c>
-      <c r="R223" t="n">
-        <v>0.7970001648357945</v>
-      </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="P223" t="n">
+        <v>4</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN223" t="b">
+        <v>1</v>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39668,12 +39668,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -39707,95 +39707,81 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>19</v>
+        <v>228</v>
       </c>
       <c r="O224" t="n">
-        <v>19</v>
+        <v>228</v>
       </c>
       <c r="R224" t="n">
-        <v>0.3379737424641861</v>
+        <v>0.8374010948505122</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="AA224" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ224" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS224" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -39822,7 +39808,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -39871,98 +39857,23 @@
       <c r="O225" t="n">
         <v>19</v>
       </c>
+      <c r="R225" t="n">
+        <v>0.3379737424641861</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U225" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
-      <c r="V225" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="W225" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X225" t="inlineStr">
-        <is>
-          <t>Streptococcus pneumoniae</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD225" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE225" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF225" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG225" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH225" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI225" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ225" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK225" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
-        </is>
-      </c>
-      <c r="AM225" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN225" t="b">
-        <v>1</v>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
@@ -40056,17 +39967,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -40100,81 +40011,170 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O226" t="n">
-        <v>17</v>
-      </c>
-      <c r="R226" t="n">
-        <v>0.03294548870446478</v>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Streptococcus pneumoniae</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
+        <v>1</v>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
       <c r="AT226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -40206,12 +40206,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -40245,95 +40245,81 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="O227" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="R227" t="n">
-        <v>0.4776234729647867</v>
+        <v>0.03875939847584092</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA227" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ227" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr"/>
       <c r="AT227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -40360,7 +40346,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -40409,98 +40395,23 @@
       <c r="O228" t="n">
         <v>27</v>
       </c>
+      <c r="R228" t="n">
+        <v>0.4776234729647867</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U228" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
-      <c r="V228" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W228" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X228" t="inlineStr">
-        <is>
-          <t>Syst. pneumokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y228" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD228" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE228" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF228" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG228" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH228" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI228" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ228" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK228" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
-        </is>
-      </c>
-      <c r="AM228" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN228" t="b">
-        <v>1</v>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
@@ -40594,17 +40505,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -40638,81 +40549,170 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="O229" t="n">
-        <v>2</v>
-      </c>
-      <c r="R229" t="n">
-        <v>0.008691384892873792</v>
-      </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>Syst. pneumokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
+        </is>
+      </c>
+      <c r="AM229" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN229" t="b">
+        <v>1</v>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR229" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -40744,12 +40744,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -40783,13 +40783,13 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="O230" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="R230" t="n">
-        <v>0.01919575548955488</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -40822,42 +40822,42 @@
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -40889,12 +40889,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -40919,7 +40919,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -40928,13 +40928,13 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="O231" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="R231" t="n">
-        <v>0.02450425222697299</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
@@ -40967,42 +40967,42 @@
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -41034,12 +41034,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -41073,93 +41073,81 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="O232" t="n">
-        <v>1</v>
-      </c>
-      <c r="P232" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="R232" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.02450425222697299</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA232" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41186,7 +41174,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -41238,98 +41226,18 @@
       <c r="P233" t="n">
         <v>1</v>
       </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W233" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X233" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y233" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R233" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB233" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD233" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE233" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF233" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG233" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH233" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ233" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK233" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM233" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN233" t="b">
-        <v>1</v>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
@@ -41423,17 +41331,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -41458,7 +41366,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -41467,81 +41375,173 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="O234" t="n">
-        <v>58</v>
-      </c>
-      <c r="R234" t="n">
-        <v>0.01661722117006243</v>
-      </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P234" t="n">
+        <v>1</v>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN234" t="b">
+        <v>1</v>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41573,12 +41573,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -41603,7 +41603,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -41612,13 +41612,13 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="O235" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="R235" t="n">
-        <v>0.01470255133618379</v>
+        <v>0.01661722117006243</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -41651,42 +41651,42 @@
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -41718,12 +41718,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -41757,93 +41757,81 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O236" t="n">
-        <v>2</v>
-      </c>
-      <c r="P236" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="R236" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.01470255133618379</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA236" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ236" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41870,7 +41858,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -41922,98 +41910,18 @@
       <c r="P237" t="n">
         <v>2</v>
       </c>
-      <c r="U237" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V237" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W237" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X237" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y237" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z237" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R237" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB237" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD237" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE237" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF237" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG237" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH237" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI237" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ237" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK237" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM237" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN237" t="b">
-        <v>1</v>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
@@ -42107,17 +42015,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -42142,7 +42050,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -42151,81 +42059,173 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="O238" t="n">
-        <v>76</v>
-      </c>
-      <c r="R238" t="n">
-        <v>0.02177428980904733</v>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P238" t="n">
+        <v>2</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN238" t="b">
+        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT238" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42257,12 +42257,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -42287,7 +42287,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -42296,13 +42296,13 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="O239" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="R239" t="n">
-        <v>0.02368744381940722</v>
+        <v>0.02177428980904733</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -42335,42 +42335,42 @@
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42402,12 +42402,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -42441,93 +42441,81 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="O240" t="n">
-        <v>2</v>
-      </c>
-      <c r="P240" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="R240" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.02368744381940722</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42554,7 +42542,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -42606,98 +42594,18 @@
       <c r="P241" t="n">
         <v>2</v>
       </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R241" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE241" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG241" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM241" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN241" t="b">
-        <v>1</v>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
@@ -42791,123 +42699,360 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N242" t="n">
+        <v>2</v>
+      </c>
+      <c r="O242" t="n">
+        <v>2</v>
+      </c>
+      <c r="P242" t="n">
+        <v>2</v>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN242" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO242" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP242" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT242" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU242" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV242" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA242" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB242" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC242" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
+      <c r="F243" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
+      <c r="G243" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>D106</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>Invasive pneumococcal disease</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
         <is>
           <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
+      <c r="K243" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
+      <c r="L243" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="M242" t="inlineStr">
+      <c r="M243" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N242" t="n">
+      <c r="N243" t="n">
         <v>52</v>
       </c>
-      <c r="O242" t="n">
+      <c r="O243" t="n">
         <v>52</v>
       </c>
-      <c r="R242" t="n">
+      <c r="R243" t="n">
         <v>0.0148981982904008</v>
       </c>
-      <c r="S242" t="inlineStr">
+      <c r="S243" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO242" t="inlineStr">
+      <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP242" t="inlineStr">
+      <c r="AP243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR242" t="inlineStr">
+      <c r="AR243" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS242" t="inlineStr"/>
-      <c r="AT242" t="n">
+      <c r="AS243" t="inlineStr"/>
+      <c r="AT243" t="n">
         <v>0</v>
       </c>
-      <c r="AU242" t="inlineStr">
+      <c r="AU243" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV242" t="inlineStr">
+      <c r="AV243" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW242" t="inlineStr">
+      <c r="AW243" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX242" t="inlineStr">
+      <c r="AX243" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY242" t="inlineStr">
+      <c r="AY243" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ242" t="inlineStr">
+      <c r="AZ243" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA242" t="inlineStr">
+      <c r="BA243" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB242" t="inlineStr">
+      <c r="BB243" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC242" t="inlineStr">
+      <c r="BC243" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -43029,7 +43174,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10">
@@ -43039,7 +43184,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -43091,7 +43236,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11800</v>
+        <v>11829</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1481,17 +1481,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1707,7 +1712,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1715,17 +1720,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2156,7 +2166,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2164,17 +2174,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2390,7 +2405,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2398,17 +2413,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2945,7 +2965,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -2953,17 +2973,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3179,7 +3204,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3187,17 +3212,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -7077,7 +7107,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7085,17 +7115,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -7311,7 +7346,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -7319,17 +7354,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -7760,7 +7800,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -7768,17 +7808,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -7994,7 +8039,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -8002,17 +8047,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8549,7 +8599,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -8557,17 +8607,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -8783,7 +8838,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -8791,17 +8846,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -12533,7 +12593,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -12541,17 +12601,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS69" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -12767,7 +12832,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -12775,17 +12840,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -13216,7 +13286,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
@@ -13224,17 +13294,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS73" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -13450,7 +13525,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
@@ -13458,17 +13533,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS74" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -14005,7 +14085,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -14013,17 +14093,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS77" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -14239,7 +14324,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
@@ -14247,17 +14332,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS78" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -18380,7 +18470,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
@@ -18388,17 +18478,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS102" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -18614,7 +18709,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
@@ -18622,17 +18717,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS103" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -19063,7 +19163,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
@@ -19071,17 +19171,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS106" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -19297,7 +19402,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
@@ -19305,17 +19410,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS107" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -19849,7 +19959,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
@@ -19857,17 +19967,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS110" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -20083,7 +20198,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
@@ -20091,17 +20206,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS111" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -23827,7 +23947,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
@@ -23835,17 +23955,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS133" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -24061,7 +24186,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
@@ -24069,17 +24194,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS134" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -24510,7 +24640,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
@@ -24518,17 +24648,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS137" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -24744,7 +24879,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
@@ -24752,17 +24887,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS138" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -25296,7 +25436,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
@@ -25304,17 +25444,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS141" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -25530,7 +25675,7 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
@@ -25538,17 +25683,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS142" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -29961,7 +30111,7 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ168" t="inlineStr">
@@ -29969,17 +30119,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS168" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -30195,7 +30350,7 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ169" t="inlineStr">
@@ -30203,17 +30358,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS169" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
@@ -30644,7 +30804,7 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
@@ -30652,17 +30812,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS172" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
@@ -30878,7 +31043,7 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
@@ -30886,17 +31051,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS173" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -31430,7 +31600,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
@@ -31438,17 +31608,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS176" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -31664,7 +31839,7 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
@@ -31672,17 +31847,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS177" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
@@ -34849,7 +35029,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
@@ -34857,17 +35037,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS196" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
@@ -35083,7 +35268,7 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
@@ -35091,17 +35276,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS197" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
@@ -35532,7 +35722,7 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
@@ -35540,17 +35730,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS200" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
@@ -35766,7 +35961,7 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
@@ -35774,17 +35969,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS201" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
@@ -36318,7 +36518,7 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ204" t="inlineStr">
@@ -36326,17 +36526,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS204" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
@@ -36552,7 +36757,7 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ205" t="inlineStr">
@@ -36560,17 +36765,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS205" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
       <c r="AT205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
@@ -39707,13 +39917,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O224" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="R224" t="n">
-        <v>0.8374010948505122</v>
+        <v>0.8484195303090715</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -39882,7 +40092,7 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
@@ -39890,17 +40100,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS225" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
@@ -40116,7 +40331,7 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
@@ -40124,17 +40339,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS226" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
@@ -40420,7 +40640,7 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
@@ -40428,17 +40648,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS228" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
@@ -40654,7 +40879,7 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
@@ -40662,17 +40887,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS229" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
@@ -43236,7 +43466,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11829</v>
+        <v>11832</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -41908,13 +41908,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="O238" t="n">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="R238" t="n">
-        <v>0.9879863794508235</v>
+        <v>1.021041685826502</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -42905,13 +42905,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O245" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R245" t="n">
-        <v>0.4091261092987516</v>
+        <v>0.4447022927160344</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -43069,10 +43069,10 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O246" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U246" t="inlineStr">
         <is>
@@ -46882,13 +46882,13 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O268" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R268" t="n">
-        <v>0.007345623639039581</v>
+        <v>0.01469124727807916</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12756</v>
+        <v>12769</v>
       </c>
     </row>
     <row r="16">
